--- a/OutData/cycle/model_BRB_fit_8.50e+03/ModelManager.xlsx
+++ b/OutData/cycle/model_BRB_fit_8.50e+03/ModelManager.xlsx
@@ -693,13 +693,9 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>pier_2_surf</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
     </row>
@@ -713,7 +709,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -729,7 +725,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -745,7 +741,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -757,11 +753,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -777,7 +773,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -793,7 +789,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -805,11 +801,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -825,7 +821,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -837,11 +833,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -853,11 +849,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -869,11 +865,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>uniaxialMaterial</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -885,11 +881,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -905,7 +901,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -917,11 +913,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>uniaxialMaterial</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -933,11 +929,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>beamIntegration</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -953,7 +949,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -965,11 +961,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -981,17 +977,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>31</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>PT_1</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
     </row>
@@ -1001,17 +993,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>28</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>pier_1_ED_2</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
     </row>
@@ -1025,7 +1013,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -1037,13 +1025,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>pier_2_surf</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
     </row>
@@ -1053,11 +1045,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>beamIntegration</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -1069,11 +1061,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -1085,13 +1077,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>pier_1_ED_2</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
     </row>
@@ -1105,7 +1101,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -1121,7 +1117,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -1137,7 +1133,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -1149,23 +1145,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>uniaxialMaterial</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>pier_2_ED_2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>{'fy': 1860000.0, 'Es': 195000000.0, 'force': 744000.0, 'yield': 0.009538461538461539}</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1173,13 +1165,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>53</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>pier_1_ED_1</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
     </row>
@@ -1189,11 +1185,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -1205,17 +1201,13 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>32</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PT_2</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
     </row>
@@ -1229,7 +1221,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -1245,7 +1237,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -1261,7 +1253,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -1277,9 +1269,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>43</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PT_2</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
     </row>
@@ -1293,7 +1289,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -1305,11 +1301,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>uniaxialMaterial</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -1325,7 +1321,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -1337,11 +1333,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -1357,7 +1353,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -1373,7 +1369,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -1389,7 +1385,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -1405,7 +1401,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -1417,11 +1413,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>uniaxialMaterial</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -1433,11 +1429,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -1453,7 +1449,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -1465,11 +1461,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>uniaxialMaterial</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -1481,13 +1477,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PT_1</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
     </row>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -1513,11 +1513,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -1593,17 +1593,13 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>30</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>pier_2_ED_2</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
     </row>
@@ -1617,7 +1613,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -1629,11 +1625,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>uniaxialMaterial</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -1645,11 +1641,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -1661,11 +1657,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -1677,11 +1673,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>beamIntegration</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -1697,7 +1693,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -1713,7 +1709,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -1729,7 +1725,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -1745,7 +1741,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -1757,11 +1753,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -1777,7 +1773,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -1789,11 +1785,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>uniaxialMaterial</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -1805,11 +1801,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -1825,7 +1821,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -1841,7 +1837,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -1857,13 +1853,9 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>37</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>pier_1_surf</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
     </row>
@@ -1877,7 +1869,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -1889,13 +1881,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>pier_1_surf</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
     </row>
@@ -1905,15 +1901,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>uniaxialMaterial</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>43</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>{'fy': 1860000.0, 'Es': 195000000.0, 'force': 744000.0, 'yield': 0.009538461538461539}</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1921,11 +1925,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -1937,11 +1941,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -1953,11 +1957,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -1969,17 +1973,13 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>disp_ctrl</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
     </row>
@@ -1989,11 +1989,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -2089,13 +2089,9 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>29</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>pier_2_ED_1</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
     </row>
@@ -2105,15 +2101,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>pier_1_ED_1</t>
+          <t>disp_ctrl</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -2125,11 +2121,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -2145,7 +2141,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -2157,11 +2153,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -2177,7 +2173,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
@@ -2189,11 +2185,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -2209,7 +2205,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
@@ -2221,11 +2217,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -2241,7 +2237,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
@@ -2253,11 +2249,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -2269,23 +2265,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>uniaxialMaterial</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>8</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>ED</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>{'fy': 637300.0, 'Es': 201000000.0, 'area': 0.00011309733552923255, 'yield': 0.003170646766169154}</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2297,7 +2285,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -2309,11 +2297,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>beamIntegration</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -2325,11 +2313,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
@@ -2341,11 +2329,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
@@ -2361,7 +2349,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
@@ -2373,7 +2361,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2389,11 +2377,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
@@ -2409,7 +2397,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
@@ -2421,15 +2409,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>uniaxialMaterial</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>16</v>
-      </c>
-      <c r="D117" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>{'fy': 637300.0, 'Es': 201000000.0, 'area': 0.00011309733552923255, 'yield': 0.003170646766169154}</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2437,11 +2433,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>uniaxialMaterial</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
@@ -2457,9 +2453,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
-      </c>
-      <c r="D119" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>pier_2_ED_1</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
     </row>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
@@ -2501,11 +2501,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
@@ -2533,11 +2533,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -2681,13 +2681,9 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>53</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>brb_top</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
     </row>
@@ -2697,11 +2693,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>beamIntegration</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
@@ -2713,11 +2709,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -2729,11 +2725,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>beamIntegration</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -2745,11 +2741,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>beamIntegration</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
@@ -2761,11 +2757,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>beamIntegration</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
@@ -2777,11 +2773,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
@@ -2793,17 +2789,13 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>56</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>brb_base</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
     </row>
@@ -2813,11 +2805,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
@@ -2833,9 +2825,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>51</v>
-      </c>
-      <c r="D140" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>brb_top</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
     </row>
@@ -2845,13 +2841,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>57</v>
-      </c>
-      <c r="D141" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>brb_base</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
     </row>
@@ -2861,11 +2861,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>node</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
